--- a/data/FAQ_ASSISTANT_QUESTIONS.xlsx
+++ b/data/FAQ_ASSISTANT_QUESTIONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sap-my.sharepoint.com/personal/andreas_forster_sap_com/Documents/CoE/My Content/2025_02 FAQ Chatbot/1 Notebooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{6C6ACA40-5B3E-49FD-9ED9-797C8CF94AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{133F4F75-5902-43F2-8A88-83528C40C8E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7AEAE4-3E5D-42A9-AB3E-7D0B22B8859D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21CE9D15-0980-4A64-8C99-96CDED0B1C72}"/>
+    <workbookView xWindow="13455" yWindow="3600" windowWidth="15555" windowHeight="11250" xr2:uid="{21CE9D15-0980-4A64-8C99-96CDED0B1C72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -191,12 +191,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -493,7 +489,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E14E89-F325-4691-9BB5-52F50068D9AB}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="77.140625" customWidth="1"/>
   </cols>
@@ -525,7 +521,7 @@
         <v>1001</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -536,7 +532,7 @@
         <v>1002</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -547,7 +543,7 @@
         <v>1003</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -558,7 +554,7 @@
         <v>1004</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -569,7 +565,7 @@
         <v>1005</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -580,7 +576,7 @@
         <v>1006</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -591,7 +587,7 @@
         <v>1007</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -602,7 +598,7 @@
         <v>1008</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -613,7 +609,7 @@
         <v>1009</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>27</v>
@@ -624,7 +620,7 @@
         <v>1010</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -635,7 +631,7 @@
         <v>1011</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -646,7 +642,7 @@
         <v>1012</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -657,7 +653,7 @@
         <v>1013</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -668,7 +664,7 @@
         <v>1014</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -679,7 +675,7 @@
         <v>1015</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -690,7 +686,7 @@
         <v>1016</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -701,7 +697,7 @@
         <v>1017</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -712,7 +708,7 @@
         <v>1018</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -723,7 +719,7 @@
         <v>1019</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -734,7 +730,7 @@
         <v>1020</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -745,7 +741,7 @@
         <v>1021</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -756,7 +752,7 @@
         <v>1022</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
@@ -767,7 +763,7 @@
         <v>1023</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
@@ -778,7 +774,7 @@
         <v>1001</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
@@ -789,7 +785,7 @@
         <v>1005</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>28</v>
@@ -800,7 +796,7 @@
         <v>1005</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>29</v>

--- a/data/FAQ_ASSISTANT_QUESTIONS.xlsx
+++ b/data/FAQ_ASSISTANT_QUESTIONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique\Videos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7AEAE4-3E5D-42A9-AB3E-7D0B22B8859D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B859E526-1B7A-40B7-82EC-11D39370B891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13455" yWindow="3600" windowWidth="15555" windowHeight="11250" xr2:uid="{21CE9D15-0980-4A64-8C99-96CDED0B1C72}"/>
+    <workbookView xWindow="12570" yWindow="3330" windowWidth="15555" windowHeight="11250" xr2:uid="{21CE9D15-0980-4A64-8C99-96CDED0B1C72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>QID</t>
   </si>
@@ -116,16 +116,7 @@
     <t>Hello</t>
   </si>
   <si>
-    <t>A Applications and P Products, but what about the S?</t>
-  </si>
-  <si>
     <t>What is SAP’s purpose and overarching strategic approach to sustainability?</t>
-  </si>
-  <si>
-    <t>Who is currently on SAP's board?</t>
-  </si>
-  <si>
-    <t>Who is the current CEO of SAP?</t>
   </si>
 </sst>
 </file>
@@ -488,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E14E89-F325-4691-9BB5-52F50068D9AB}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="77.140625" customWidth="1"/>
@@ -612,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -769,38 +760,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>1001</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="27" spans="1:3">
-      <c r="A27">
-        <v>1005</v>
-      </c>
-      <c r="B27">
-        <v>26</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>1005</v>
-      </c>
-      <c r="B28">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>29</v>
-      </c>
+      <c r="C27" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
